--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -460,72 +460,72 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.5556</v>
+        <v>17.04364</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59069</v>
+        <v>16.36425</v>
       </c>
       <c r="E2" t="n">
-        <v>16.83774</v>
+        <v>16.83773</v>
       </c>
       <c r="F2" t="n">
-        <v>41.99945</v>
+        <v>42.03395</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05056</v>
+        <v>0.05061</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82244</v>
+        <v>1.83569</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.62733</v>
+        <v>16.95184</v>
       </c>
       <c r="D3" t="n">
-        <v>17.02729</v>
+        <v>16.41232</v>
       </c>
       <c r="E3" t="n">
-        <v>16.62115</v>
+        <v>16.72289</v>
       </c>
       <c r="F3" t="n">
-        <v>43.62935</v>
+        <v>42.84563</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04949</v>
+        <v>0.0504</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81184</v>
+        <v>1.86102</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.84248</v>
+        <v>16.86843</v>
       </c>
       <c r="D4" t="n">
-        <v>16.6442</v>
+        <v>16.50505</v>
       </c>
       <c r="E4" t="n">
-        <v>16.78493</v>
+        <v>16.77169</v>
       </c>
       <c r="F4" t="n">
-        <v>42.64702</v>
+        <v>41.96326</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05025</v>
+        <v>0.0511</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79929</v>
+        <v>1.80463</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.81812</v>
+        <v>16.80133</v>
       </c>
       <c r="D5" t="n">
-        <v>16.41476</v>
+        <v>16.5713</v>
       </c>
       <c r="E5" t="n">
-        <v>16.94019</v>
+        <v>16.73142</v>
       </c>
       <c r="F5" t="n">
-        <v>41.90391</v>
+        <v>43.04954</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05011</v>
+        <v>0.05139</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79914</v>
+        <v>1.82042</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.73905</v>
+        <v>16.75952</v>
       </c>
       <c r="D6" t="n">
-        <v>17.09993</v>
+        <v>16.52482</v>
       </c>
       <c r="E6" t="n">
-        <v>17.04923</v>
+        <v>16.72473</v>
       </c>
       <c r="F6" t="n">
-        <v>42.6984</v>
+        <v>41.92013</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05028</v>
+        <v>0.05148</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81752</v>
+        <v>1.84919</v>
       </c>
     </row>
     <row r="7">
@@ -585,1285 +585,1596 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.67962</v>
+        <v>16.68752</v>
       </c>
       <c r="D7" t="n">
-        <v>16.89611</v>
+        <v>16.42478</v>
       </c>
       <c r="E7" t="n">
-        <v>16.74151</v>
+        <v>16.58498</v>
       </c>
       <c r="F7" t="n">
-        <v>42.52238</v>
+        <v>42.37302</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05057</v>
+        <v>0.05015</v>
       </c>
       <c r="H7" t="n">
-        <v>1.78651</v>
+        <v>1.82532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.96219</v>
+        <v>16.81668</v>
       </c>
       <c r="D8" t="n">
-        <v>16.91775</v>
+        <v>16.61557</v>
       </c>
       <c r="E8" t="n">
-        <v>16.65532</v>
+        <v>16.64859</v>
       </c>
       <c r="F8" t="n">
-        <v>42.14593</v>
+        <v>42.39424</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05097</v>
+        <v>0.05005</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82988</v>
+        <v>1.82355</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.63345</v>
+        <v>16.94996</v>
       </c>
       <c r="D9" t="n">
-        <v>16.67493</v>
+        <v>16.44384</v>
       </c>
       <c r="E9" t="n">
-        <v>16.8495</v>
+        <v>16.74651</v>
       </c>
       <c r="F9" t="n">
-        <v>43.23624</v>
+        <v>42.53639</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0503</v>
+        <v>0.05084</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82572</v>
+        <v>1.84709</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.86412</v>
+        <v>16.74418</v>
       </c>
       <c r="D10" t="n">
-        <v>16.46211</v>
+        <v>16.65005</v>
       </c>
       <c r="E10" t="n">
-        <v>16.92819</v>
+        <v>16.68499</v>
       </c>
       <c r="F10" t="n">
-        <v>42.06734</v>
+        <v>42.92388</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05067</v>
+        <v>0.05049</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81326</v>
+        <v>1.83678</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16.65579</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.4195</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.43495</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42.84832</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.04905</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.80677</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.09494</v>
+        <v>17.13223</v>
       </c>
       <c r="D12" t="n">
-        <v>16.41686</v>
+        <v>16.67998</v>
       </c>
       <c r="E12" t="n">
-        <v>16.59263</v>
+        <v>17.04453</v>
       </c>
       <c r="F12" t="n">
-        <v>41.93163</v>
+        <v>41.98253</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05046</v>
+        <v>0.05028</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81018</v>
+        <v>1.84022</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.7525</v>
+        <v>16.656</v>
       </c>
       <c r="D13" t="n">
-        <v>16.31201</v>
+        <v>16.47137</v>
       </c>
       <c r="E13" t="n">
-        <v>16.67054</v>
+        <v>16.6481</v>
       </c>
       <c r="F13" t="n">
-        <v>42.50795</v>
+        <v>41.60237</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05107</v>
+        <v>0.04993</v>
       </c>
       <c r="H13" t="n">
-        <v>1.80769</v>
+        <v>1.8197</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.65165</v>
+        <v>17.19335</v>
       </c>
       <c r="D14" t="n">
-        <v>16.77832</v>
+        <v>16.56606</v>
       </c>
       <c r="E14" t="n">
-        <v>16.51951</v>
+        <v>16.67059</v>
       </c>
       <c r="F14" t="n">
-        <v>42.54966</v>
+        <v>41.62274</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05133</v>
+        <v>0.05046</v>
       </c>
       <c r="H14" t="n">
-        <v>1.80506</v>
+        <v>1.80538</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.63151</v>
+        <v>17.18816</v>
       </c>
       <c r="D15" t="n">
-        <v>16.57773</v>
+        <v>16.73659</v>
       </c>
       <c r="E15" t="n">
-        <v>16.6816</v>
+        <v>16.89704</v>
       </c>
       <c r="F15" t="n">
-        <v>43.25351</v>
+        <v>42.33624</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05072</v>
+        <v>0.05039</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8356</v>
+        <v>1.79679</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.99587</v>
+        <v>17.06466</v>
       </c>
       <c r="D16" t="n">
-        <v>16.37397</v>
+        <v>16.57663</v>
       </c>
       <c r="E16" t="n">
-        <v>16.79319</v>
+        <v>16.75223</v>
       </c>
       <c r="F16" t="n">
-        <v>42.45474</v>
+        <v>42.23541</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05067</v>
+        <v>0.05098</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78428</v>
+        <v>1.80927</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.85547</v>
+        <v>17.17543</v>
       </c>
       <c r="D17" t="n">
-        <v>16.58026</v>
+        <v>16.57351</v>
       </c>
       <c r="E17" t="n">
-        <v>16.85798</v>
+        <v>16.60131</v>
       </c>
       <c r="F17" t="n">
-        <v>42.57174</v>
+        <v>42.74265</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05017</v>
+        <v>0.05064</v>
       </c>
       <c r="H17" t="n">
-        <v>1.79717</v>
+        <v>1.80216</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.74295</v>
+        <v>16.75219</v>
       </c>
       <c r="D18" t="n">
-        <v>16.74016</v>
+        <v>16.37932</v>
       </c>
       <c r="E18" t="n">
-        <v>16.9122</v>
+        <v>16.48593</v>
       </c>
       <c r="F18" t="n">
-        <v>42.16575</v>
+        <v>41.77383</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05155</v>
+        <v>0.05088</v>
       </c>
       <c r="H18" t="n">
-        <v>1.79829</v>
+        <v>1.81367</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.83738</v>
+        <v>16.85204</v>
       </c>
       <c r="D19" t="n">
-        <v>16.87068</v>
+        <v>16.75685</v>
       </c>
       <c r="E19" t="n">
-        <v>16.66902</v>
+        <v>16.85168</v>
       </c>
       <c r="F19" t="n">
-        <v>42.51021</v>
+        <v>41.64738</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05019</v>
+        <v>0.05083</v>
       </c>
       <c r="H19" t="n">
-        <v>1.83575</v>
+        <v>1.8545</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.20069</v>
+        <v>16.80556</v>
       </c>
       <c r="D20" t="n">
-        <v>16.93249</v>
+        <v>16.45023</v>
       </c>
       <c r="E20" t="n">
-        <v>16.74097</v>
+        <v>16.6765</v>
       </c>
       <c r="F20" t="n">
-        <v>42.42248</v>
+        <v>41.28934</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05077</v>
+        <v>0.04919</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7674</v>
+        <v>1.78557</v>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>16.87273</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16.28743</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16.55461</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42.66692</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.05094</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.86426</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SR Pad 1</t>
+          <t>Unit 21</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.45985</v>
+        <v>16.89059</v>
       </c>
       <c r="D22" t="n">
-        <v>15.77414</v>
+        <v>16.74101</v>
       </c>
       <c r="E22" t="n">
-        <v>15.95434</v>
+        <v>16.87715</v>
       </c>
       <c r="F22" t="n">
-        <v>255.81838</v>
+        <v>42.10243</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.05103</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.80838</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 22</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.78421</v>
+        <v>16.85371</v>
       </c>
       <c r="D23" t="n">
-        <v>15.45016</v>
+        <v>16.59235</v>
       </c>
       <c r="E23" t="n">
-        <v>15.7824</v>
+        <v>16.76238</v>
       </c>
       <c r="F23" t="n">
-        <v>256.09108</v>
+        <v>42.32632</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.04967</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.80762</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 23</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.75931</v>
+        <v>17.03437</v>
       </c>
       <c r="D24" t="n">
-        <v>15.65596</v>
+        <v>16.42844</v>
       </c>
       <c r="E24" t="n">
-        <v>15.76243</v>
+        <v>16.81054</v>
       </c>
       <c r="F24" t="n">
-        <v>254.5973</v>
+        <v>42.41748</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.81679</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 24</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.77803</v>
+        <v>16.8201</v>
       </c>
       <c r="D25" t="n">
-        <v>15.87108</v>
+        <v>16.51002</v>
       </c>
       <c r="E25" t="n">
-        <v>15.44747</v>
+        <v>16.76155</v>
       </c>
       <c r="F25" t="n">
-        <v>252.08134</v>
+        <v>41.65677</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.04923</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.84074</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 25</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.65851</v>
+        <v>16.90677</v>
       </c>
       <c r="D26" t="n">
-        <v>15.33454</v>
+        <v>16.27901</v>
       </c>
       <c r="E26" t="n">
-        <v>15.85541</v>
+        <v>16.81518</v>
       </c>
       <c r="F26" t="n">
-        <v>254.09001</v>
+        <v>41.98681</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05054</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.80313</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 26</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15.44687</v>
+        <v>16.90062</v>
       </c>
       <c r="D27" t="n">
-        <v>15.71478</v>
+        <v>16.51789</v>
       </c>
       <c r="E27" t="n">
-        <v>15.57308</v>
+        <v>16.62599</v>
       </c>
       <c r="F27" t="n">
-        <v>254.80082</v>
+        <v>42.75831</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.05124</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.85055</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.29018</v>
+        <v>17.06274</v>
       </c>
       <c r="D28" t="n">
-        <v>15.52789</v>
+        <v>16.60363</v>
       </c>
       <c r="E28" t="n">
-        <v>15.68228</v>
+        <v>16.70052</v>
       </c>
       <c r="F28" t="n">
-        <v>251.90029</v>
+        <v>42.44487</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.05006</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.83495</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 28</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.81787</v>
+        <v>17.00527</v>
       </c>
       <c r="D29" t="n">
-        <v>15.84346</v>
+        <v>16.10242</v>
       </c>
       <c r="E29" t="n">
-        <v>15.53635</v>
+        <v>16.66592</v>
       </c>
       <c r="F29" t="n">
-        <v>257.80518</v>
+        <v>43.31612</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.81467</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 29</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.52088</v>
+        <v>16.86716</v>
       </c>
       <c r="D30" t="n">
-        <v>15.82891</v>
+        <v>16.51912</v>
       </c>
       <c r="E30" t="n">
-        <v>15.36592</v>
+        <v>16.62728</v>
       </c>
       <c r="F30" t="n">
-        <v>257.11551</v>
+        <v>42.89732</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05079</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.81281</v>
       </c>
     </row>
     <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>16.88093</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16.61036</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.73421</v>
+      </c>
+      <c r="F31" t="n">
+        <v>43.20097</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.05126</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.82755</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
+          <t>Unit 31</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.63761</v>
+        <v>16.65948</v>
       </c>
       <c r="D32" t="n">
-        <v>16.0521</v>
+        <v>16.45113</v>
       </c>
       <c r="E32" t="n">
-        <v>16.26884</v>
+        <v>16.60623</v>
       </c>
       <c r="F32" t="n">
-        <v>21.87334</v>
+        <v>42.57492</v>
       </c>
       <c r="G32" t="n">
-        <v>33.6682</v>
+        <v>0.05085</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.83474</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 32</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.76682</v>
+        <v>16.57037</v>
       </c>
       <c r="D33" t="n">
-        <v>16.01289</v>
+        <v>16.43134</v>
       </c>
       <c r="E33" t="n">
-        <v>16.19453</v>
+        <v>16.54411</v>
       </c>
       <c r="F33" t="n">
-        <v>21.58468</v>
+        <v>42.78987</v>
       </c>
       <c r="G33" t="n">
-        <v>33.72821</v>
+        <v>0.05051</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.84668</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 33</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.70683</v>
+        <v>16.69522</v>
       </c>
       <c r="D34" t="n">
-        <v>16.07452</v>
+        <v>16.45084</v>
       </c>
       <c r="E34" t="n">
-        <v>16.35837</v>
+        <v>16.67848</v>
       </c>
       <c r="F34" t="n">
-        <v>21.76139</v>
+        <v>42.87644</v>
       </c>
       <c r="G34" t="n">
-        <v>34.49787</v>
+        <v>0.05055</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.78443</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 34</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.55547</v>
+        <v>16.87678</v>
       </c>
       <c r="D35" t="n">
-        <v>16.13221</v>
+        <v>16.34644</v>
       </c>
       <c r="E35" t="n">
-        <v>16.47785</v>
+        <v>16.63858</v>
       </c>
       <c r="F35" t="n">
-        <v>21.18457</v>
+        <v>42.86811</v>
       </c>
       <c r="G35" t="n">
-        <v>34.16907</v>
+        <v>0.05107</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.82835</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 35</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.56375</v>
+        <v>17.03609</v>
       </c>
       <c r="D36" t="n">
-        <v>15.86463</v>
+        <v>16.62458</v>
       </c>
       <c r="E36" t="n">
-        <v>16.43219</v>
+        <v>16.95297</v>
       </c>
       <c r="F36" t="n">
-        <v>21.40131</v>
+        <v>41.99969</v>
       </c>
       <c r="G36" t="n">
-        <v>35.38803</v>
+        <v>0.05029</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.77711</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 36</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.66271</v>
+        <v>17.06228</v>
       </c>
       <c r="D37" t="n">
-        <v>16.13483</v>
+        <v>16.79354</v>
       </c>
       <c r="E37" t="n">
-        <v>16.78</v>
+        <v>16.92475</v>
       </c>
       <c r="F37" t="n">
-        <v>21.37913</v>
+        <v>42.59016</v>
       </c>
       <c r="G37" t="n">
-        <v>34.11929</v>
+        <v>0.05127</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.82565</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>16.51111</v>
-      </c>
-      <c r="D38" t="n">
-        <v>16.36777</v>
-      </c>
-      <c r="E38" t="n">
-        <v>16.49621</v>
-      </c>
-      <c r="F38" t="n">
-        <v>21.76782</v>
-      </c>
-      <c r="G38" t="n">
-        <v>34.82194</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.46223</v>
+        <v>16.59906</v>
       </c>
       <c r="D39" t="n">
-        <v>15.78565</v>
+        <v>15.68367</v>
       </c>
       <c r="E39" t="n">
-        <v>16.45778</v>
+        <v>16.47699</v>
       </c>
       <c r="F39" t="n">
-        <v>21.72856</v>
+        <v>21.34624</v>
       </c>
       <c r="G39" t="n">
-        <v>34.62215</v>
+        <v>34.04253</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.34278</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.58271</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.32038</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.78371</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.83195</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>16.75798</v>
-      </c>
-      <c r="D40" t="n">
-        <v>15.8281</v>
-      </c>
-      <c r="E40" t="n">
-        <v>16.37044</v>
-      </c>
-      <c r="F40" t="n">
-        <v>21.56373</v>
-      </c>
-      <c r="G40" t="n">
-        <v>33.73775</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="C41" t="n">
+        <v>16.52552</v>
+      </c>
+      <c r="D41" t="n">
+        <v>15.84956</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16.17497</v>
+      </c>
+      <c r="F41" t="n">
+        <v>21.9195</v>
+      </c>
+      <c r="G41" t="n">
+        <v>33.85629</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Trace 2</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17.04153</v>
+        <v>16.75954</v>
       </c>
       <c r="D42" t="n">
-        <v>15.7752</v>
+        <v>16.01146</v>
       </c>
       <c r="E42" t="n">
-        <v>16.32184</v>
+        <v>16.58575</v>
       </c>
       <c r="F42" t="n">
-        <v>21.8057</v>
+        <v>21.21988</v>
       </c>
       <c r="G42" t="n">
-        <v>33.56438</v>
+        <v>34.22932</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16.53544</v>
+        <v>16.82736</v>
       </c>
       <c r="D43" t="n">
-        <v>16.16978</v>
+        <v>15.88023</v>
       </c>
       <c r="E43" t="n">
-        <v>16.3066</v>
+        <v>16.20332</v>
       </c>
       <c r="F43" t="n">
-        <v>21.98121</v>
+        <v>21.81377</v>
       </c>
       <c r="G43" t="n">
-        <v>34.60433</v>
+        <v>33.50168</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16.88719</v>
+        <v>16.78391</v>
       </c>
       <c r="D44" t="n">
-        <v>16.06809</v>
+        <v>16.05703</v>
       </c>
       <c r="E44" t="n">
-        <v>16.35435</v>
+        <v>16.44264</v>
       </c>
       <c r="F44" t="n">
-        <v>21.69997</v>
+        <v>21.75872</v>
       </c>
       <c r="G44" t="n">
-        <v>34.48091</v>
+        <v>34.62558</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.8098</v>
+        <v>16.59434</v>
       </c>
       <c r="D45" t="n">
-        <v>16.12324</v>
+        <v>16.04611</v>
       </c>
       <c r="E45" t="n">
-        <v>16.24852</v>
+        <v>16.48611</v>
       </c>
       <c r="F45" t="n">
-        <v>21.92443</v>
+        <v>21.56764</v>
       </c>
       <c r="G45" t="n">
-        <v>34.37942</v>
+        <v>33.97148</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.84229</v>
+        <v>16.44034</v>
       </c>
       <c r="D46" t="n">
-        <v>15.95159</v>
+        <v>15.95374</v>
       </c>
       <c r="E46" t="n">
-        <v>16.28976</v>
+        <v>16.42586</v>
       </c>
       <c r="F46" t="n">
-        <v>21.0671</v>
+        <v>21.77674</v>
       </c>
       <c r="G46" t="n">
-        <v>34.31569</v>
+        <v>33.99173</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.95695</v>
+        <v>16.57668</v>
       </c>
       <c r="D47" t="n">
-        <v>16.027</v>
+        <v>16.16899</v>
       </c>
       <c r="E47" t="n">
-        <v>16.25354</v>
+        <v>16.26756</v>
       </c>
       <c r="F47" t="n">
-        <v>22.1159</v>
+        <v>22.12303</v>
       </c>
       <c r="G47" t="n">
-        <v>34.47042</v>
+        <v>34.52336</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.51884</v>
+        <v>16.61987</v>
       </c>
       <c r="D48" t="n">
-        <v>16.02485</v>
+        <v>15.98493</v>
       </c>
       <c r="E48" t="n">
-        <v>16.57526</v>
+        <v>16.37275</v>
       </c>
       <c r="F48" t="n">
-        <v>21.73887</v>
+        <v>21.99075</v>
       </c>
       <c r="G48" t="n">
-        <v>34.54553</v>
+        <v>34.21316</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.93157</v>
+        <v>16.83303</v>
       </c>
       <c r="D49" t="n">
-        <v>15.98008</v>
+        <v>16.02667</v>
       </c>
       <c r="E49" t="n">
-        <v>16.43843</v>
+        <v>16.03404</v>
       </c>
       <c r="F49" t="n">
-        <v>21.61892</v>
+        <v>21.95391</v>
       </c>
       <c r="G49" t="n">
-        <v>33.95164</v>
+        <v>34.22828</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>16.91344</v>
+        <v>16.44588</v>
       </c>
       <c r="D50" t="n">
-        <v>16.03541</v>
+        <v>15.80807</v>
       </c>
       <c r="E50" t="n">
-        <v>16.23374</v>
+        <v>16.35253</v>
       </c>
       <c r="F50" t="n">
-        <v>21.97975</v>
+        <v>21.6183</v>
       </c>
       <c r="G50" t="n">
-        <v>35.23817</v>
+        <v>34.89509</v>
       </c>
     </row>
     <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>17.11902</v>
+      </c>
+      <c r="D51" t="n">
+        <v>15.79528</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.19884</v>
+      </c>
+      <c r="F51" t="n">
+        <v>21.42362</v>
+      </c>
+      <c r="G51" t="n">
+        <v>33.57509</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.61703</v>
+        <v>16.76829</v>
       </c>
       <c r="D52" t="n">
-        <v>1.10098</v>
+        <v>15.86468</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.62383</v>
+      </c>
+      <c r="F52" t="n">
+        <v>21.9906</v>
+      </c>
+      <c r="G52" t="n">
+        <v>33.83599</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.61498</v>
+        <v>16.74462</v>
       </c>
       <c r="D53" t="n">
-        <v>1.08126</v>
+        <v>15.62888</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.43005</v>
+      </c>
+      <c r="F53" t="n">
+        <v>21.85872</v>
+      </c>
+      <c r="G53" t="n">
+        <v>34.31077</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.60922</v>
+        <v>16.53438</v>
       </c>
       <c r="D54" t="n">
-        <v>1.11</v>
+        <v>15.98461</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.44491</v>
+      </c>
+      <c r="F54" t="n">
+        <v>21.22261</v>
+      </c>
+      <c r="G54" t="n">
+        <v>34.49437</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.5980799999999999</v>
+        <v>16.57005</v>
       </c>
       <c r="D55" t="n">
-        <v>1.12269</v>
+        <v>15.96675</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.54096</v>
+      </c>
+      <c r="F55" t="n">
+        <v>21.54846</v>
+      </c>
+      <c r="G55" t="n">
+        <v>34.65736</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.60668</v>
+        <v>16.74012</v>
       </c>
       <c r="D56" t="n">
-        <v>1.08203</v>
+        <v>16.22465</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.73281</v>
+      </c>
+      <c r="F56" t="n">
+        <v>22.40296</v>
+      </c>
+      <c r="G56" t="n">
+        <v>33.47585</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.61369</v>
+        <v>17.02433</v>
       </c>
       <c r="D57" t="n">
-        <v>1.1202</v>
+        <v>16.24605</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.36331</v>
+      </c>
+      <c r="F57" t="n">
+        <v>21.777</v>
+      </c>
+      <c r="G57" t="n">
+        <v>34.1788</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.60148</v>
+        <v>16.74635</v>
       </c>
       <c r="D58" t="n">
-        <v>1.10591</v>
+        <v>16.23356</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.33749</v>
+      </c>
+      <c r="F58" t="n">
+        <v>21.29772</v>
+      </c>
+      <c r="G58" t="n">
+        <v>34.91775</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 21</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.60811</v>
+        <v>16.85402</v>
       </c>
       <c r="D59" t="n">
-        <v>1.10455</v>
+        <v>15.68172</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.42348</v>
+      </c>
+      <c r="F59" t="n">
+        <v>21.49982</v>
+      </c>
+      <c r="G59" t="n">
+        <v>34.44621</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 22</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.60729</v>
+        <v>16.74743</v>
       </c>
       <c r="D60" t="n">
-        <v>1.12185</v>
+        <v>16.11413</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.26966</v>
+      </c>
+      <c r="F60" t="n">
+        <v>21.81214</v>
+      </c>
+      <c r="G60" t="n">
+        <v>34.03597</v>
       </c>
     </row>
     <row r="61">
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>16.58592</v>
+      </c>
+      <c r="D61" t="n">
+        <v>16.23446</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.45369</v>
+      </c>
+      <c r="F61" t="n">
+        <v>21.29557</v>
+      </c>
+      <c r="G61" t="n">
+        <v>34.33774</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>via 2</t>
+          <t>Unit 24</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.59887</v>
+        <v>16.59305</v>
       </c>
       <c r="D62" t="n">
-        <v>1.08224</v>
+        <v>15.89958</v>
+      </c>
+      <c r="E62" t="n">
+        <v>16.09385</v>
+      </c>
+      <c r="F62" t="n">
+        <v>21.67488</v>
+      </c>
+      <c r="G62" t="n">
+        <v>33.63006</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 25</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.62796</v>
+        <v>17.10853</v>
       </c>
       <c r="D63" t="n">
-        <v>1.10448</v>
+        <v>15.99974</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16.41109</v>
+      </c>
+      <c r="F63" t="n">
+        <v>22.07751</v>
+      </c>
+      <c r="G63" t="n">
+        <v>34.22693</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 26</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.60939</v>
+        <v>16.62814</v>
       </c>
       <c r="D64" t="n">
-        <v>1.10506</v>
+        <v>16.36619</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16.56169</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21.60792</v>
+      </c>
+      <c r="G64" t="n">
+        <v>34.17944</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 27</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.58883</v>
+        <v>16.8051</v>
       </c>
       <c r="D65" t="n">
-        <v>1.14225</v>
+        <v>15.94636</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16.47231</v>
+      </c>
+      <c r="F65" t="n">
+        <v>21.6843</v>
+      </c>
+      <c r="G65" t="n">
+        <v>34.23459</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 28</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.60345</v>
+        <v>16.59011</v>
       </c>
       <c r="D66" t="n">
-        <v>1.11596</v>
+        <v>15.81542</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.06809</v>
+      </c>
+      <c r="F66" t="n">
+        <v>22.02382</v>
+      </c>
+      <c r="G66" t="n">
+        <v>34.753</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 29</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.61546</v>
+        <v>16.75435</v>
       </c>
       <c r="D67" t="n">
-        <v>1.12282</v>
+        <v>15.7264</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.36216</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.58409</v>
+      </c>
+      <c r="G67" t="n">
+        <v>33.89973</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 30</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.59617</v>
+        <v>17.03262</v>
       </c>
       <c r="D68" t="n">
-        <v>1.09834</v>
+        <v>16.10728</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16.4753</v>
+      </c>
+      <c r="F68" t="n">
+        <v>22.05394</v>
+      </c>
+      <c r="G68" t="n">
+        <v>34.15828</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 31</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.60278</v>
+        <v>16.63119</v>
       </c>
       <c r="D69" t="n">
-        <v>1.09127</v>
+        <v>16.06161</v>
+      </c>
+      <c r="E69" t="n">
+        <v>16.59198</v>
+      </c>
+      <c r="F69" t="n">
+        <v>21.90578</v>
+      </c>
+      <c r="G69" t="n">
+        <v>34.45024</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 32</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.6140600000000001</v>
+        <v>16.44679</v>
       </c>
       <c r="D70" t="n">
-        <v>1.10608</v>
+        <v>16.05677</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16.34277</v>
+      </c>
+      <c r="F70" t="n">
+        <v>21.10562</v>
+      </c>
+      <c r="G70" t="n">
+        <v>34.85977</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>16.87804</v>
+      </c>
+      <c r="D71" t="n">
+        <v>16.0063</v>
+      </c>
+      <c r="E71" t="n">
+        <v>16.47463</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21.78815</v>
+      </c>
+      <c r="G71" t="n">
+        <v>34.36418</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16.36662</v>
+      </c>
+      <c r="D72" t="n">
+        <v>16.21389</v>
+      </c>
+      <c r="E72" t="n">
+        <v>16.28576</v>
+      </c>
+      <c r="F72" t="n">
+        <v>21.97181</v>
+      </c>
+      <c r="G72" t="n">
+        <v>34.61673</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>16.69983</v>
+      </c>
+      <c r="D73" t="n">
+        <v>15.79945</v>
+      </c>
+      <c r="E73" t="n">
+        <v>16.3977</v>
+      </c>
+      <c r="F73" t="n">
+        <v>21.80267</v>
+      </c>
+      <c r="G73" t="n">
+        <v>33.7118</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>16.88025</v>
+      </c>
+      <c r="D74" t="n">
+        <v>16.109</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16.11046</v>
+      </c>
+      <c r="F74" t="n">
+        <v>22.06228</v>
+      </c>
+      <c r="G74" t="n">
+        <v>33.50689</v>
       </c>
     </row>
   </sheetData>
